--- a/data/macro/Japan/Japan CPI YoY.xlsx
+++ b/data/macro/Japan/Japan CPI YoY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\Japan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F440DBFB-2CC4-4514-B629-78639EC5D149}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB26919D-CE7C-436A-B8AB-8463AB332D8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5235" yWindow="1575" windowWidth="28800" windowHeight="16995" xr2:uid="{A0358DA5-9C11-4628-B2D7-24F5FD1145D7}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="12">
   <si>
     <t>Release Date</t>
   </si>
@@ -77,8 +77,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="181" formatCode="0.0%"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="0.0%"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -179,16 +179,16 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F546E751-EA49-4715-8697-66309DE54846}">
-  <dimension ref="A1:H662"/>
+  <dimension ref="A1:H663"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.7109375" style="5" bestFit="1" customWidth="1"/>
@@ -14163,8 +14163,28 @@
       <c r="D662" s="7" t="s">
         <v>11</v>
       </c>
+      <c r="E662" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
       <c r="G662" s="13">
         <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="663" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A663" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B663" s="5">
+        <v>45740</v>
+      </c>
+      <c r="C663" s="11">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D663" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G663" s="13">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/macro/Japan/Japan CPI YoY.xlsx
+++ b/data/macro/Japan/Japan CPI YoY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\Japan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\Japan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB26919D-CE7C-436A-B8AB-8463AB332D8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260D0B9E-066B-4A8C-A6C4-78B01F631BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5235" yWindow="1575" windowWidth="28800" windowHeight="16995" xr2:uid="{A0358DA5-9C11-4628-B2D7-24F5FD1145D7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0358DA5-9C11-4628-B2D7-24F5FD1145D7}"/>
   </bookViews>
   <sheets>
     <sheet name="JPCPI YoY" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="12">
   <si>
     <t>Release Date</t>
   </si>
@@ -506,20 +506,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F546E751-EA49-4715-8697-66309DE54846}">
-  <dimension ref="A1:H663"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H664"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="14.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="14.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="4"/>
+    <col min="8" max="8" width="11.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -542,7 +542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>25934</v>
       </c>
@@ -560,7 +560,7 @@
       </c>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>25965</v>
       </c>
@@ -581,7 +581,7 @@
       </c>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>25993</v>
       </c>
@@ -602,7 +602,7 @@
       </c>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>26024</v>
       </c>
@@ -623,7 +623,7 @@
       </c>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>26054</v>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>26085</v>
       </c>
@@ -665,7 +665,7 @@
       </c>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>26115</v>
       </c>
@@ -686,7 +686,7 @@
       </c>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>26146</v>
       </c>
@@ -707,7 +707,7 @@
       </c>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>26177</v>
       </c>
@@ -728,7 +728,7 @@
       </c>
       <c r="H10" s="8"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>26207</v>
       </c>
@@ -749,7 +749,7 @@
       </c>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>26238</v>
       </c>
@@ -770,7 +770,7 @@
       </c>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>26268</v>
       </c>
@@ -791,7 +791,7 @@
       </c>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>26299</v>
       </c>
@@ -811,7 +811,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>26330</v>
       </c>
@@ -831,7 +831,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>26359</v>
       </c>
@@ -851,7 +851,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>26390</v>
       </c>
@@ -871,7 +871,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>26420</v>
       </c>
@@ -891,7 +891,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>26451</v>
       </c>
@@ -911,7 +911,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>26481</v>
       </c>
@@ -931,7 +931,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>26512</v>
       </c>
@@ -951,7 +951,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>26543</v>
       </c>
@@ -971,7 +971,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>26573</v>
       </c>
@@ -991,7 +991,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>26604</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>26634</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>26665</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>26696</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>26724</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>26755</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>26785</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26816</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>26846</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>26877</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>0.11700000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>26908</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>26938</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>26969</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>26999</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>0.152</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>27030</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>0.183</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>27061</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>0.219</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>27089</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>0.249</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>27120</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>0.22800000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>27150</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>0.23699999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>27181</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>27211</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>0.223</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>27242</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>0.23799999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>27273</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>0.23899999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>27303</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>27334</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>0.248</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>27364</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>0.245</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>27395</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>27426</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>0.16800000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>27454</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>27485</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>27515</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>0.13400000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>27546</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>27576</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>0.13400000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>27607</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>27638</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>27668</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>27699</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>27729</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>27760</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>27791</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>27820</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>27851</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>27881</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>27912</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>27942</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>27973</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>28004</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>28034</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>28065</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>28095</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>28126</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>28157</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>28185</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>28216</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>28246</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>28277</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>28307</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>28338</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>28369</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>28399</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>28430</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>28460</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>28491</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>28522</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>28550</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>28581</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>28611</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>28642</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>28672</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>28703</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>28734</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>28764</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>28795</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>28825</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>28856</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>28887</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>28915</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>28946</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>28976</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>29007</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>29037</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>29068</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>29099</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>29129</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>29160</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>29190</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>29221</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>29252</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>29281</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>29312</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>29342</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>29373</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
         <v>29403</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>29434</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="5">
         <v>29465</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>29495</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="5">
         <v>29526</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>29556</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>29587</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>29618</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
         <v>29646</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>29677</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
         <v>29707</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>29738</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>29768</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>29799</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="5">
         <v>29830</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
         <v>29860</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
         <v>29891</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>29921</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>29952</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>29983</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>30011</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="5">
         <v>30042</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>30072</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="5">
         <v>30103</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="5">
         <v>30133</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="5">
         <v>30164</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="5">
         <v>30195</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="5">
         <v>30225</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="5">
         <v>30256</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="5">
         <v>30286</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="5">
         <v>30317</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="5">
         <v>30348</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>30376</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="5">
         <v>30407</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="5">
         <v>30437</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="5">
         <v>30468</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>30498</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>30529</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="5">
         <v>30560</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>30590</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>30621</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>30651</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>30682</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>30713</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
         <v>30742</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>30773</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="5">
         <v>30803</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="5">
         <v>30834</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="5">
         <v>30864</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
         <v>30895</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
         <v>30926</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
         <v>30956</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="5">
         <v>30987</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
         <v>31017</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>31048</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>31079</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>31107</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>31138</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="5">
         <v>31168</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="5">
         <v>31199</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="5">
         <v>31229</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="5">
         <v>31260</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="5">
         <v>31291</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="5">
         <v>31321</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="5">
         <v>31352</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="5">
         <v>31382</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="5">
         <v>31413</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="5">
         <v>31444</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="5">
         <v>31472</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="5">
         <v>31503</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="5">
         <v>31533</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="5">
         <v>31564</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="5">
         <v>31594</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="5">
         <v>31625</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="5">
         <v>31656</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="5">
         <v>31686</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="5">
         <v>31717</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="5">
         <v>31747</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="5">
         <v>31778</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="5">
         <v>31809</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="5">
         <v>31837</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="5">
         <v>31868</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="5">
         <v>31898</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="5">
         <v>31929</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="5">
         <v>31959</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="5">
         <v>31990</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="5">
         <v>32021</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="5">
         <v>32051</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="5">
         <v>32082</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="5">
         <v>32112</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="5">
         <v>32143</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="5">
         <v>32174</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="5">
         <v>32203</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="5">
         <v>32234</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="5">
         <v>32264</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="5">
         <v>32295</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="5">
         <v>32325</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="5">
         <v>32356</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="5">
         <v>32387</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="5">
         <v>32417</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="5">
         <v>32448</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="5">
         <v>32478</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="5">
         <v>32509</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="5">
         <v>32540</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="5">
         <v>32568</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="5">
         <v>32599</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="5">
         <v>32629</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="5">
         <v>32660</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="5">
         <v>32690</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="5">
         <v>32721</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="5">
         <v>32752</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="5">
         <v>32782</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="5">
         <v>32813</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="5">
         <v>32843</v>
       </c>
@@ -5111,7 +5111,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="5">
         <v>32874</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="5">
         <v>32905</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="5">
         <v>32933</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="5">
         <v>32964</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="5">
         <v>32994</v>
       </c>
@@ -5211,7 +5211,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="5">
         <v>33025</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="5">
         <v>33055</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="5">
         <v>33086</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="5">
         <v>33117</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="5">
         <v>33147</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="5">
         <v>33178</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="5">
         <v>33208</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="5">
         <v>33239</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="5">
         <v>33270</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="5">
         <v>33298</v>
       </c>
@@ -5411,7 +5411,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="5">
         <v>33329</v>
       </c>
@@ -5431,7 +5431,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="5">
         <v>33359</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="5">
         <v>33390</v>
       </c>
@@ -5471,7 +5471,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="5">
         <v>33420</v>
       </c>
@@ -5491,7 +5491,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="5">
         <v>33451</v>
       </c>
@@ -5511,7 +5511,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="5">
         <v>33482</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="5">
         <v>33512</v>
       </c>
@@ -5551,7 +5551,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="5">
         <v>33543</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="5">
         <v>33573</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="5">
         <v>33604</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="5">
         <v>33635</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="5">
         <v>33664</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="5">
         <v>33695</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="5">
         <v>33725</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="5">
         <v>33756</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="5">
         <v>33786</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="5">
         <v>33817</v>
       </c>
@@ -5751,7 +5751,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="5">
         <v>33848</v>
       </c>
@@ -5771,7 +5771,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="5">
         <v>33878</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="5">
         <v>33909</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="5">
         <v>33939</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="5">
         <v>33970</v>
       </c>
@@ -5851,7 +5851,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="5">
         <v>34001</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="5">
         <v>34029</v>
       </c>
@@ -5891,7 +5891,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="5">
         <v>34060</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="5">
         <v>34090</v>
       </c>
@@ -5931,7 +5931,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="5">
         <v>34121</v>
       </c>
@@ -5951,7 +5951,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="5">
         <v>34151</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="5">
         <v>34182</v>
       </c>
@@ -5991,7 +5991,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="5">
         <v>34213</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="5">
         <v>34243</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="5">
         <v>34274</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="5">
         <v>34304</v>
       </c>
@@ -6071,7 +6071,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="5">
         <v>34335</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="5">
         <v>34366</v>
       </c>
@@ -6111,7 +6111,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="5">
         <v>34394</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="5">
         <v>34425</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="5">
         <v>34455</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="5">
         <v>34486</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="5">
         <v>34516</v>
       </c>
@@ -6211,7 +6211,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="5">
         <v>34547</v>
       </c>
@@ -6231,7 +6231,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="5">
         <v>34578</v>
       </c>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" s="5">
         <v>34608</v>
       </c>
@@ -6271,7 +6271,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="5">
         <v>34639</v>
       </c>
@@ -6291,7 +6291,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="5">
         <v>34669</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" s="5">
         <v>34700</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" s="5">
         <v>34731</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="5">
         <v>34759</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" s="5">
         <v>34790</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" s="5">
         <v>34820</v>
       </c>
@@ -6411,7 +6411,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" s="5">
         <v>34851</v>
       </c>
@@ -6431,7 +6431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" s="5">
         <v>34881</v>
       </c>
@@ -6451,7 +6451,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="5">
         <v>34912</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="5">
         <v>34943</v>
       </c>
@@ -6491,7 +6491,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="5">
         <v>34973</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="5">
         <v>35004</v>
       </c>
@@ -6531,7 +6531,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="5">
         <v>35034</v>
       </c>
@@ -6551,7 +6551,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" s="5">
         <v>35065</v>
       </c>
@@ -6571,7 +6571,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" s="5">
         <v>35096</v>
       </c>
@@ -6591,7 +6591,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" s="5">
         <v>35125</v>
       </c>
@@ -6611,7 +6611,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" s="5">
         <v>35156</v>
       </c>
@@ -6631,7 +6631,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306" s="5">
         <v>35186</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307" s="5">
         <v>35217</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308" s="5">
         <v>35247</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309" s="5">
         <v>35278</v>
       </c>
@@ -6711,7 +6711,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310" s="5">
         <v>35309</v>
       </c>
@@ -6731,7 +6731,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311" s="5">
         <v>35339</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312" s="5">
         <v>35370</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313" s="5">
         <v>35400</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314" s="5">
         <v>35431</v>
       </c>
@@ -6811,7 +6811,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315" s="5">
         <v>35462</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316" s="5">
         <v>35490</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317" s="5">
         <v>35521</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318" s="5">
         <v>35551</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319" s="5">
         <v>35582</v>
       </c>
@@ -6911,7 +6911,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320" s="5">
         <v>35612</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321" s="5">
         <v>35643</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322" s="5">
         <v>35674</v>
       </c>
@@ -6971,7 +6971,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A323" s="5">
         <v>35704</v>
       </c>
@@ -6991,7 +6991,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324" s="5">
         <v>35735</v>
       </c>
@@ -7011,7 +7011,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A325" s="5">
         <v>35765</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A326" s="5">
         <v>35796</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A327" s="5">
         <v>35827</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A328" s="5">
         <v>35855</v>
       </c>
@@ -7091,7 +7091,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A329" s="5">
         <v>35886</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A330" s="5">
         <v>35916</v>
       </c>
@@ -7131,7 +7131,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A331" s="5">
         <v>35947</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A332" s="5">
         <v>35977</v>
       </c>
@@ -7171,7 +7171,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A333" s="5">
         <v>36008</v>
       </c>
@@ -7191,7 +7191,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A334" s="5">
         <v>36039</v>
       </c>
@@ -7211,7 +7211,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A335" s="5">
         <v>36069</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A336" s="5">
         <v>36100</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A337" s="5">
         <v>36130</v>
       </c>
@@ -7271,7 +7271,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A338" s="5">
         <v>36161</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A339" s="5">
         <v>36192</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A340" s="5">
         <v>36220</v>
       </c>
@@ -7331,7 +7331,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A341" s="5">
         <v>36251</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A342" s="5">
         <v>36281</v>
       </c>
@@ -7371,7 +7371,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A343" s="5">
         <v>36312</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A344" s="5">
         <v>36342</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A345" s="5">
         <v>36373</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A346" s="5">
         <v>36404</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A347" s="5">
         <v>36434</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A348" s="5">
         <v>36465</v>
       </c>
@@ -7491,7 +7491,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A349" s="5">
         <v>36495</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A350" s="5">
         <v>36526</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A351" s="5">
         <v>36557</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A352" s="5">
         <v>36586</v>
       </c>
@@ -7571,7 +7571,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A353" s="5">
         <v>36617</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A354" s="5">
         <v>36647</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A355" s="5">
         <v>36678</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A356" s="5">
         <v>36708</v>
       </c>
@@ -7651,7 +7651,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A357" s="5">
         <v>36739</v>
       </c>
@@ -7671,7 +7671,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A358" s="5">
         <v>36770</v>
       </c>
@@ -7691,7 +7691,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A359" s="5">
         <v>36800</v>
       </c>
@@ -7711,7 +7711,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A360" s="5">
         <v>36831</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A361" s="5">
         <v>36861</v>
       </c>
@@ -7751,7 +7751,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A362" s="5">
         <v>36892</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A363" s="5">
         <v>36923</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A364" s="5">
         <v>36951</v>
       </c>
@@ -7811,7 +7811,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A365" s="5">
         <v>36982</v>
       </c>
@@ -7831,7 +7831,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A366" s="5">
         <v>37012</v>
       </c>
@@ -7851,7 +7851,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A367" s="5">
         <v>37043</v>
       </c>
@@ -7871,7 +7871,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A368" s="5">
         <v>37073</v>
       </c>
@@ -7891,7 +7891,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A369" s="5">
         <v>37104</v>
       </c>
@@ -7911,7 +7911,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A370" s="5">
         <v>37135</v>
       </c>
@@ -7931,7 +7931,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A371" s="5">
         <v>37165</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A372" s="5">
         <v>37196</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A373" s="5">
         <v>37226</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A374" s="5">
         <v>37257</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A375" s="5">
         <v>37288</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A376" s="5">
         <v>37316</v>
       </c>
@@ -8051,7 +8051,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A377" s="5">
         <v>37347</v>
       </c>
@@ -8071,7 +8071,7 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A378" s="5">
         <v>37377</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A379" s="5">
         <v>37408</v>
       </c>
@@ -8111,7 +8111,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A380" s="5">
         <v>37438</v>
       </c>
@@ -8131,7 +8131,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A381" s="5">
         <v>37469</v>
       </c>
@@ -8151,7 +8151,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A382" s="5">
         <v>37500</v>
       </c>
@@ -8171,7 +8171,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A383" s="5">
         <v>37530</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A384" s="5">
         <v>37561</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A385" s="5">
         <v>37591</v>
       </c>
@@ -8231,7 +8231,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A386" s="5">
         <v>37622</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A387" s="5">
         <v>37653</v>
       </c>
@@ -8271,7 +8271,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A388" s="5">
         <v>37681</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A389" s="5">
         <v>37712</v>
       </c>
@@ -8311,7 +8311,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A390" s="5">
         <v>37742</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A391" s="5">
         <v>37773</v>
       </c>
@@ -8351,7 +8351,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A392" s="5">
         <v>37803</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A393" s="5">
         <v>37834</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A394" s="5">
         <v>37865</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A395" s="5">
         <v>37895</v>
       </c>
@@ -8431,7 +8431,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A396" s="5">
         <v>37926</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A397" s="5">
         <v>37956</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A398" s="5">
         <v>37987</v>
       </c>
@@ -8491,7 +8491,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A399" s="5">
         <v>38018</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A400" s="5">
         <v>38047</v>
       </c>
@@ -8531,7 +8531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A401" s="5">
         <v>38078</v>
       </c>
@@ -8551,7 +8551,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A402" s="5">
         <v>38108</v>
       </c>
@@ -8571,7 +8571,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A403" s="5">
         <v>38139</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A404" s="5">
         <v>38169</v>
       </c>
@@ -8611,7 +8611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A405" s="5">
         <v>38200</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A406" s="5">
         <v>38231</v>
       </c>
@@ -8651,7 +8651,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A407" s="5">
         <v>38261</v>
       </c>
@@ -8671,7 +8671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A408" s="5">
         <v>38292</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A409" s="5">
         <v>38322</v>
       </c>
@@ -8711,7 +8711,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A410" s="5">
         <v>38353</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A411" s="5">
         <v>38384</v>
       </c>
@@ -8751,7 +8751,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A412" s="5">
         <v>38412</v>
       </c>
@@ -8771,7 +8771,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A413" s="5">
         <v>38443</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A414" s="5">
         <v>38473</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A415" s="5">
         <v>38504</v>
       </c>
@@ -8831,7 +8831,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A416" s="5">
         <v>38534</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A417" s="5">
         <v>38565</v>
       </c>
@@ -8871,7 +8871,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A418" s="5">
         <v>38596</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A419" s="5">
         <v>38626</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A420" s="5">
         <v>38657</v>
       </c>
@@ -8931,7 +8931,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A421" s="5">
         <v>38687</v>
       </c>
@@ -8951,7 +8951,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A422" s="5">
         <v>38718</v>
       </c>
@@ -8971,7 +8971,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A423" s="5">
         <v>38749</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A424" s="5">
         <v>38777</v>
       </c>
@@ -9011,7 +9011,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A425" s="5">
         <v>38808</v>
       </c>
@@ -9031,7 +9031,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A426" s="5">
         <v>38838</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A427" s="5">
         <v>38869</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A428" s="5">
         <v>38899</v>
       </c>
@@ -9091,7 +9091,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A429" s="5">
         <v>38930</v>
       </c>
@@ -9111,7 +9111,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A430" s="5">
         <v>38961</v>
       </c>
@@ -9131,7 +9131,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A431" s="5">
         <v>38991</v>
       </c>
@@ -9151,7 +9151,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A432" s="5">
         <v>39022</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A433" s="5">
         <v>39052</v>
       </c>
@@ -9191,7 +9191,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A434" s="5">
         <v>39083</v>
       </c>
@@ -9211,7 +9211,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A435" s="5">
         <v>39114</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A436" s="5">
         <v>39142</v>
       </c>
@@ -9251,7 +9251,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A437" s="5">
         <v>39173</v>
       </c>
@@ -9271,7 +9271,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A438" s="5">
         <v>39203</v>
       </c>
@@ -9291,7 +9291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A439" s="5">
         <v>39234</v>
       </c>
@@ -9311,7 +9311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A440" s="5">
         <v>39264</v>
       </c>
@@ -9331,7 +9331,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A441" s="5">
         <v>39295</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A442" s="5">
         <v>39326</v>
       </c>
@@ -9371,7 +9371,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A443" s="5">
         <v>39356</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A444" s="5">
         <v>39387</v>
       </c>
@@ -9411,7 +9411,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A445" s="5">
         <v>39417</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A446" s="5">
         <v>39448</v>
       </c>
@@ -9451,7 +9451,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A447" s="5">
         <v>39479</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A448" s="5">
         <v>39508</v>
       </c>
@@ -9491,7 +9491,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A449" s="5">
         <v>39539</v>
       </c>
@@ -9511,7 +9511,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A450" s="5">
         <v>39569</v>
       </c>
@@ -9531,7 +9531,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A451" s="5">
         <v>39600</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A452" s="5">
         <v>39630</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A453" s="5">
         <v>39661</v>
       </c>
@@ -9591,7 +9591,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A454" s="5">
         <v>39692</v>
       </c>
@@ -9611,7 +9611,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A455" s="5">
         <v>39722</v>
       </c>
@@ -9631,7 +9631,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A456" s="5">
         <v>39753</v>
       </c>
@@ -9651,7 +9651,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A457" s="5">
         <v>39783</v>
       </c>
@@ -9671,7 +9671,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A458" s="5">
         <v>39814</v>
       </c>
@@ -9691,7 +9691,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A459" s="5">
         <v>39845</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A460" s="5">
         <v>39873</v>
       </c>
@@ -9731,7 +9731,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A461" s="5">
         <v>39904</v>
       </c>
@@ -9751,7 +9751,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A462" s="5">
         <v>39934</v>
       </c>
@@ -9771,7 +9771,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A463" s="5">
         <v>39965</v>
       </c>
@@ -9791,7 +9791,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A464" s="5">
         <v>39995</v>
       </c>
@@ -9811,7 +9811,7 @@
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A465" s="5">
         <v>40026</v>
       </c>
@@ -9831,7 +9831,7 @@
         <v>-2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A466" s="5">
         <v>40057</v>
       </c>
@@ -9851,7 +9851,7 @@
         <v>-2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A467" s="5">
         <v>40087</v>
       </c>
@@ -9871,7 +9871,7 @@
         <v>-2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A468" s="5">
         <v>40118</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>-2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A469" s="5">
         <v>40148</v>
       </c>
@@ -9911,7 +9911,7 @@
         <v>-1.9E-2</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A470" s="5">
         <v>40179</v>
       </c>
@@ -9931,7 +9931,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A471" s="5">
         <v>40210</v>
       </c>
@@ -9951,7 +9951,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A472" s="5">
         <v>40238</v>
       </c>
@@ -9971,7 +9971,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A473" s="5">
         <v>40269</v>
       </c>
@@ -9991,7 +9991,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A474" s="5">
         <v>40299</v>
       </c>
@@ -10011,7 +10011,7 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A475" s="5">
         <v>40330</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A476" s="5">
         <v>40360</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A477" s="5">
         <v>40391</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A478" s="5">
         <v>40422</v>
       </c>
@@ -10091,7 +10091,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A479" s="5">
         <v>40452</v>
       </c>
@@ -10111,7 +10111,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A480" s="5">
         <v>40483</v>
       </c>
@@ -10131,7 +10131,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A481" s="5">
         <v>40513</v>
       </c>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="H481" s="9"/>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A482" s="5">
         <v>40544</v>
       </c>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="H482" s="9"/>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A483" s="5">
         <v>40575</v>
       </c>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="H483" s="9"/>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A484" s="5">
         <v>40603</v>
       </c>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="H484" s="9"/>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A485" s="5">
         <v>40634</v>
       </c>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="H485" s="9"/>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A486" s="5">
         <v>40664</v>
       </c>
@@ -10257,7 +10257,7 @@
       </c>
       <c r="H486" s="9"/>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A487" s="5">
         <v>40695</v>
       </c>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="H487" s="9"/>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A488" s="5">
         <v>40725</v>
       </c>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="H488" s="9"/>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A489" s="5">
         <v>40756</v>
       </c>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="H489" s="9"/>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A490" s="5">
         <v>40787</v>
       </c>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="H490" s="9"/>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A491" s="5">
         <v>40817</v>
       </c>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="H491" s="9"/>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A492" s="5">
         <v>40848</v>
       </c>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="H492" s="9"/>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A493" s="5">
         <v>40878</v>
       </c>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="H493" s="9"/>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A494" s="5">
         <v>40909</v>
       </c>
@@ -10425,7 +10425,7 @@
       </c>
       <c r="H494" s="9"/>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A495" s="5">
         <v>40940</v>
       </c>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="H495" s="9"/>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A496" s="5">
         <v>40969</v>
       </c>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="H496" s="9"/>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A497" s="5">
         <v>41000</v>
       </c>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="H497" s="9"/>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A498" s="5">
         <v>41030</v>
       </c>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="H498" s="9"/>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A499" s="5">
         <v>41061</v>
       </c>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="H499" s="9"/>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A500" s="5">
         <v>41091</v>
       </c>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="H500" s="9"/>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A501" s="5">
         <v>41122</v>
       </c>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="H501" s="9"/>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A502" s="5">
         <v>41153</v>
       </c>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="H502" s="9"/>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A503" s="5">
         <v>41183</v>
       </c>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H503" s="9"/>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A504" s="5">
         <v>41214</v>
       </c>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="H504" s="9"/>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A505" s="5">
         <v>41244</v>
       </c>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="H505" s="9"/>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A506" s="5">
         <v>41275</v>
       </c>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="H506" s="9"/>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A507" s="5">
         <v>41306</v>
       </c>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="H507" s="9"/>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A508" s="5">
         <v>41334</v>
       </c>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="H508" s="9"/>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A509" s="5">
         <v>41365</v>
       </c>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H509" s="9"/>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A510" s="5">
         <v>41395</v>
       </c>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="H510" s="9"/>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A511" s="5">
         <v>41426</v>
       </c>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="H511" s="9"/>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A512" s="5">
         <v>41456</v>
       </c>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="H512" s="9"/>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A513" s="5">
         <v>41487</v>
       </c>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="H513" s="9"/>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A514" s="5">
         <v>41518</v>
       </c>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="H514" s="9"/>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A515" s="5">
         <v>41548</v>
       </c>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="H515" s="9"/>
     </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A516" s="5">
         <v>41579</v>
       </c>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="H516" s="9"/>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A517" s="5">
         <v>41609</v>
       </c>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H517" s="9"/>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A518" s="5">
         <v>41640</v>
       </c>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="H518" s="9"/>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A519" s="5">
         <v>41671</v>
       </c>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="H519" s="9"/>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A520" s="5">
         <v>41699</v>
       </c>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="H520" s="9"/>
     </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A521" s="5">
         <v>41730</v>
       </c>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="H521" s="9"/>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A522" s="5">
         <v>41760</v>
       </c>
@@ -11031,7 +11031,7 @@
       </c>
       <c r="H522" s="9"/>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A523" s="5">
         <v>41791</v>
       </c>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="H523" s="9"/>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A524" s="5">
         <v>41821</v>
       </c>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="H524" s="9"/>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A525" s="5">
         <v>41852</v>
       </c>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="H525" s="9"/>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A526" s="5">
         <v>41883</v>
       </c>
@@ -11121,7 +11121,7 @@
       </c>
       <c r="H526" s="9"/>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A527" s="5">
         <v>41913</v>
       </c>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="H527" s="9"/>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A528" s="5">
         <v>41944</v>
       </c>
@@ -11166,7 +11166,7 @@
       </c>
       <c r="H528" s="9"/>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A529" s="5">
         <v>41974</v>
       </c>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="H529" s="9"/>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A530" s="5">
         <v>42005</v>
       </c>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="H530" s="9"/>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A531" s="5">
         <v>42036</v>
       </c>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="H531" s="9"/>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A532" s="5">
         <v>42064</v>
       </c>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="H532" s="9"/>
     </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A533" s="5">
         <v>42095</v>
       </c>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="H533" s="9"/>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A534" s="5">
         <v>42125</v>
       </c>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="H534" s="9"/>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A535" s="5">
         <v>42156</v>
       </c>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="H535" s="9"/>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A536" s="5">
         <v>42186</v>
       </c>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="H536" s="9"/>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A537" s="5">
         <v>42217</v>
       </c>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="H537" s="9"/>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A538" s="5">
         <v>42248</v>
       </c>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="H538" s="9"/>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A539" s="5">
         <v>42278</v>
       </c>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="H539" s="9"/>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A540" s="5">
         <v>42309</v>
       </c>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="H540" s="9"/>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A541" s="5">
         <v>42339</v>
       </c>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H541" s="9"/>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A542" s="5">
         <v>42370</v>
       </c>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="H542" s="9"/>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A543" s="5">
         <v>42401</v>
       </c>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="H543" s="9"/>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A544" s="5">
         <v>42430</v>
       </c>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="H544" s="9"/>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A545" s="5">
         <v>42461</v>
       </c>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="H545" s="9"/>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A546" s="5">
         <v>42491</v>
       </c>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="H546" s="9"/>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A547" s="5">
         <v>42522</v>
       </c>
@@ -11613,7 +11613,7 @@
       </c>
       <c r="H547" s="9"/>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A548" s="5">
         <v>42552</v>
       </c>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="H548" s="9"/>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A549" s="5">
         <v>42583</v>
       </c>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="H549" s="9"/>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A550" s="5">
         <v>42614</v>
       </c>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="H550" s="9"/>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A551" s="5">
         <v>42644</v>
       </c>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="H551" s="9"/>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A552" s="5">
         <v>42675</v>
       </c>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="H552" s="9"/>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A553" s="5">
         <v>42705</v>
       </c>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="H553" s="9"/>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A554" s="5">
         <v>42736</v>
       </c>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="H554" s="9"/>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A555" s="5">
         <v>42767</v>
       </c>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="H555" s="9"/>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A556" s="5">
         <v>42795</v>
       </c>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="H556" s="9"/>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A557" s="5">
         <v>42826</v>
       </c>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="H557" s="9"/>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A558" s="5">
         <v>42856</v>
       </c>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="H558" s="9"/>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A559" s="5">
         <v>42887</v>
       </c>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H559" s="9"/>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A560" s="5">
         <v>42917</v>
       </c>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="H560" s="9"/>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A561" s="5">
         <v>42948</v>
       </c>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="H561" s="9"/>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A562" s="5">
         <v>42979</v>
       </c>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="H562" s="9"/>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A563" s="5">
         <v>43009</v>
       </c>
@@ -11991,7 +11991,7 @@
       </c>
       <c r="H563" s="9"/>
     </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A564" s="5">
         <v>43040</v>
       </c>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="H564" s="9"/>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A565" s="5">
         <v>43070</v>
       </c>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="H565" s="9"/>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A566" s="5">
         <v>43101</v>
       </c>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="H566" s="9"/>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A567" s="5">
         <v>43132</v>
       </c>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="H567" s="9"/>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A568" s="5">
         <v>43160</v>
       </c>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="H568" s="9"/>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A569" s="5">
         <v>43191</v>
       </c>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="H569" s="9"/>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A570" s="5">
         <v>43221</v>
       </c>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="H570" s="9"/>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A571" s="5">
         <v>43252</v>
       </c>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="H571" s="9"/>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A572" s="5">
         <v>43282</v>
       </c>
@@ -12207,7 +12207,7 @@
       </c>
       <c r="H572" s="9"/>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A573" s="5">
         <v>43313</v>
       </c>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="H573" s="9"/>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A574" s="5">
         <v>43344</v>
       </c>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="H574" s="9"/>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A575" s="5">
         <v>43374</v>
       </c>
@@ -12273,7 +12273,7 @@
       </c>
       <c r="H575" s="9"/>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A576" s="5">
         <v>43405</v>
       </c>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="H576" s="9"/>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A577" s="5">
         <v>43435</v>
       </c>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="H577" s="9"/>
     </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A578" s="5">
         <v>43466</v>
       </c>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="H578" s="9"/>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A579" s="5">
         <v>43497</v>
       </c>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="H579" s="9"/>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A580" s="5">
         <v>43525</v>
       </c>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="H580" s="9"/>
     </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A581" s="5">
         <v>43556</v>
       </c>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="H581" s="9"/>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A582" s="5">
         <v>43586</v>
       </c>
@@ -12441,7 +12441,7 @@
       </c>
       <c r="H582" s="9"/>
     </row>
-    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A583" s="5">
         <v>43617</v>
       </c>
@@ -12465,7 +12465,7 @@
       </c>
       <c r="H583" s="9"/>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A584" s="5">
         <v>43647</v>
       </c>
@@ -12489,7 +12489,7 @@
       </c>
       <c r="H584" s="9"/>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A585" s="5">
         <v>43678</v>
       </c>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="H585" s="9"/>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A586" s="5">
         <v>43709</v>
       </c>
@@ -12537,7 +12537,7 @@
       </c>
       <c r="H586" s="9"/>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A587" s="5">
         <v>43739</v>
       </c>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="H587" s="9"/>
     </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A588" s="5">
         <v>43770</v>
       </c>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="H588" s="9"/>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A589" s="5">
         <v>43800</v>
       </c>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="H589" s="9"/>
     </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A590" s="5">
         <v>43831</v>
       </c>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H590" s="9"/>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A591" s="5">
         <v>43862</v>
       </c>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="H591" s="9"/>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A592" s="5">
         <v>43891</v>
       </c>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="H592" s="9"/>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A593" s="5">
         <v>43922</v>
       </c>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="H593" s="9"/>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A594" s="5">
         <v>43952</v>
       </c>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="H594" s="9"/>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A595" s="5">
         <v>43983</v>
       </c>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="H595" s="9"/>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A596" s="5">
         <v>44013</v>
       </c>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="H596" s="9"/>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A597" s="5">
         <v>44044</v>
       </c>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="H597" s="9"/>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A598" s="5">
         <v>44075</v>
       </c>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="H598" s="9"/>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A599" s="5">
         <v>44105</v>
       </c>
@@ -12822,7 +12822,7 @@
       </c>
       <c r="H599" s="9"/>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A600" s="5">
         <v>44136</v>
       </c>
@@ -12843,7 +12843,7 @@
       </c>
       <c r="H600" s="9"/>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A601" s="5">
         <v>44166</v>
       </c>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="H601" s="9"/>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A602" s="5">
         <v>44197</v>
       </c>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="H602" s="9"/>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A603" s="5">
         <v>44228</v>
       </c>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="H603" s="9"/>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A604" s="5">
         <v>44256</v>
       </c>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="H604" s="9"/>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A605" s="5">
         <v>44287</v>
       </c>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="H605" s="9"/>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A606" s="5">
         <v>44317</v>
       </c>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="H606" s="9"/>
     </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A607" s="5">
         <v>44348</v>
       </c>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="H607" s="9"/>
     </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A608" s="5">
         <v>44378</v>
       </c>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="H608" s="9"/>
     </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A609" s="5">
         <v>44409</v>
       </c>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="H609" s="9"/>
     </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A610" s="5">
         <v>44440</v>
       </c>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="H610" s="9"/>
     </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A611" s="5">
         <v>44470</v>
       </c>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="H611" s="9"/>
     </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A612" s="5">
         <v>44501</v>
       </c>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="H612" s="9"/>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A613" s="5">
         <v>44531</v>
       </c>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="H613" s="9"/>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A614" s="5">
         <v>44562</v>
       </c>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="H614" s="9"/>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A615" s="5">
         <v>44593</v>
       </c>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="H615" s="9"/>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A616" s="5">
         <v>44621</v>
       </c>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="H616" s="9"/>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A617" s="5">
         <v>44652</v>
       </c>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="H617" s="9"/>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A618" s="5">
         <v>44682</v>
       </c>
@@ -13221,7 +13221,7 @@
       </c>
       <c r="H618" s="9"/>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A619" s="5">
         <v>44713</v>
       </c>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="H619" s="9"/>
     </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A620" s="5">
         <v>44743</v>
       </c>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="H620" s="9"/>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A621" s="5">
         <v>44774</v>
       </c>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="H621" s="9"/>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A622" s="5">
         <v>44805</v>
       </c>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="H622" s="9"/>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A623" s="5">
         <v>44835</v>
       </c>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="H623" s="9"/>
     </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A624" s="5">
         <v>44866</v>
       </c>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="H624" s="9"/>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A625" s="5">
         <v>44896</v>
       </c>
@@ -13368,7 +13368,7 @@
       </c>
       <c r="H625" s="9"/>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A626" s="5">
         <v>44927</v>
       </c>
@@ -13389,7 +13389,7 @@
       </c>
       <c r="H626" s="9"/>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A627" s="5">
         <v>44958</v>
       </c>
@@ -13410,7 +13410,7 @@
       </c>
       <c r="H627" s="9"/>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A628" s="5">
         <v>44986</v>
       </c>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="H628" s="9"/>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A629" s="5">
         <v>45017</v>
       </c>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="H629" s="9"/>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A630" s="5">
         <v>45047</v>
       </c>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="H630" s="9"/>
     </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A631" s="5">
         <v>45078</v>
       </c>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="H631" s="9"/>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A632" s="5">
         <v>45108</v>
       </c>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="H632" s="9"/>
     </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A633" s="5">
         <v>45139</v>
       </c>
@@ -13551,7 +13551,7 @@
       </c>
       <c r="H633" s="9"/>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A634" s="5">
         <v>45170</v>
       </c>
@@ -13572,7 +13572,7 @@
       </c>
       <c r="H634" s="9"/>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A635" s="5">
         <v>45200</v>
       </c>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="H635" s="9"/>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A636" s="5">
         <v>45231</v>
       </c>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="H636" s="9"/>
     </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A637" s="5">
         <v>45261</v>
       </c>
@@ -13638,7 +13638,7 @@
       </c>
       <c r="H637" s="9"/>
     </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A638" s="5">
         <v>45292</v>
       </c>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="H638" s="9"/>
     </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A639" s="5">
         <v>45323</v>
       </c>
@@ -13680,7 +13680,7 @@
       </c>
       <c r="H639" s="9"/>
     </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A640" s="5">
         <v>45352</v>
       </c>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="H640" s="9"/>
     </row>
-    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A641" s="5">
         <v>45383</v>
       </c>
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H641" s="9"/>
     </row>
-    <row r="642" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A642" s="5">
         <v>45413</v>
       </c>
@@ -13746,7 +13746,7 @@
       </c>
       <c r="H642" s="9"/>
     </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A643" s="5">
         <v>45444</v>
       </c>
@@ -13767,7 +13767,7 @@
       </c>
       <c r="H643" s="9"/>
     </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A644" s="5">
         <v>45474</v>
       </c>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="H644" s="9"/>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A645" s="5">
         <v>45505</v>
       </c>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="H645" s="9"/>
     </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A646" s="5">
         <v>45536</v>
       </c>
@@ -13833,7 +13833,7 @@
       </c>
       <c r="H646" s="9"/>
     </row>
-    <row r="647" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A647" s="5">
         <v>45566</v>
       </c>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="H647" s="9"/>
     </row>
-    <row r="648" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A648" s="5">
         <v>45597</v>
       </c>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="H648" s="9"/>
     </row>
-    <row r="649" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A649" s="5">
         <v>45627</v>
       </c>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="H649" s="9"/>
     </row>
-    <row r="650" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A650" s="5">
         <v>45658</v>
       </c>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="H650" s="9"/>
     </row>
-    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A651" s="5">
         <v>45689</v>
       </c>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="H651" s="9"/>
     </row>
-    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A652" s="5">
         <v>45717</v>
       </c>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="H652" s="9"/>
     </row>
-    <row r="653" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A653" s="5">
         <v>45748</v>
       </c>
@@ -13980,7 +13980,7 @@
       </c>
       <c r="H653" s="9"/>
     </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A654" s="5">
         <v>45778</v>
       </c>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="H654" s="9"/>
     </row>
-    <row r="655" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A655" s="5">
         <v>45809</v>
       </c>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="H655" s="9"/>
     </row>
-    <row r="656" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A656" s="5">
         <v>45839</v>
       </c>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="H656" s="9"/>
     </row>
-    <row r="657" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A657" s="5">
         <v>45870</v>
       </c>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="H657" s="9"/>
     </row>
-    <row r="658" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A658" s="5">
         <v>45901</v>
       </c>
@@ -14088,7 +14088,7 @@
       </c>
       <c r="H658" s="9"/>
     </row>
-    <row r="659" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A659" s="5">
         <v>45931</v>
       </c>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="H659" s="9"/>
     </row>
-    <row r="660" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A660" s="5">
         <v>45962</v>
       </c>
@@ -14130,12 +14130,12 @@
       </c>
       <c r="H660" s="9"/>
     </row>
-    <row r="661" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A661" s="5">
         <v>45992</v>
       </c>
       <c r="B661" s="5">
-        <v>45680</v>
+        <v>46045</v>
       </c>
       <c r="C661" s="11">
         <v>0.35416666666666669</v>
@@ -14150,12 +14150,12 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="662" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A662" s="5">
         <v>46023</v>
       </c>
       <c r="B662" s="5">
-        <v>45708</v>
+        <v>46073</v>
       </c>
       <c r="C662" s="11">
         <v>0.35416666666666669</v>
@@ -14170,25 +14170,48 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="663" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A663" s="5">
         <v>46054</v>
       </c>
       <c r="B663" s="5">
-        <v>45740</v>
+        <v>46105</v>
       </c>
       <c r="C663" s="11">
         <v>0.35416666666666669</v>
       </c>
       <c r="D663" s="7" t="s">
         <v>11</v>
+      </c>
+      <c r="E663" s="13">
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="G663" s="13">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
+    <row r="664" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A664" s="5">
+        <v>46082</v>
+      </c>
+      <c r="B664" s="5">
+        <v>46136</v>
+      </c>
+      <c r="C664" s="11">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D664" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E664" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G664" s="13">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="B2:G662">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G662">
     <sortCondition ref="B2:B662"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14200,12 +14223,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7043F4AB-5389-4625-9F9F-4D4B26DB20C4}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
@@ -14213,7 +14236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
